--- a/data/trans_orig/P6907S1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6907S1-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97883</t>
+          <t>96906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107729</t>
+          <t>107647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36701</t>
+          <t>36765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130957</t>
+          <t>131373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142846</t>
+          <t>143094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16352</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>38345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51456</t>
+          <t>50079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249421</t>
+          <t>248600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>270593</t>
+          <t>269551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101463</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113562</t>
+          <t>113609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354059</t>
+          <t>355436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>379938</t>
+          <t>380170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>32143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46330</t>
+          <t>45704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>58706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107844</t>
+          <t>105915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125733</t>
+          <t>125186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>84594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>415022</t>
+          <t>414413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>440931</t>
+          <t>440013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185823</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203976</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>607833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>640204</t>
+          <t>640300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012 (tasa de respuesta: 44,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,62 +2371,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6975</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24074</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81235</t>
+          <t>81599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91386</t>
+          <t>91378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144701</t>
+          <t>144948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155391</t>
+          <t>155512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31547</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128713</t>
+          <t>127469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138749</t>
+          <t>138869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92422</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99260</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224361</t>
+          <t>223952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237048</t>
+          <t>237271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46738</t>
+          <t>46606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54560</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>64583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73605</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215675</t>
+          <t>216265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226353</t>
+          <t>226451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118637</t>
+          <t>118333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337109</t>
+          <t>337908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349709</t>
+          <t>349788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57024</t>
+          <t>57003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64124</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72779</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125377</t>
+          <t>125332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135277</t>
+          <t>135385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327971</t>
+          <t>326812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342237</t>
+          <t>341725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204528</t>
+          <t>203460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214425</t>
+          <t>214384</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>537373</t>
+          <t>537477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554564</t>
+          <t>553802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47542</t>
+          <t>47525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53466</t>
+          <t>53475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52023</t>
+          <t>52543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206967</t>
+          <t>206389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224457</t>
+          <t>225274</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213217</t>
+          <t>213566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229469</t>
+          <t>228861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425925</t>
+          <t>425405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450590</t>
+          <t>450122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63092</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68623</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83749</t>
+          <t>83570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124093</t>
+          <t>123418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144360</t>
+          <t>144219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51278</t>
+          <t>51477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>40206</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85123</t>
+          <t>82323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287042</t>
+          <t>286843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312490</t>
+          <t>312109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>312994</t>
+          <t>313843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334873</t>
+          <t>334922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>607246</t>
+          <t>610046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>641508</t>
+          <t>644261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
